--- a/sensitivity_results/legacy/multiconcept/summary_vgg16.xlsx
+++ b/sensitivity_results/legacy/multiconcept/summary_vgg16.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srikant1\Downloads\results\sensitivity_summmary\Updatedsummary\mnetsmall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEF4303-BEB5-45FE-BF70-AB6AC00C396D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F9276E-8595-4CEA-8C84-858F59C8759C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="13" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vgg16_Class_0_all" sheetId="1" r:id="rId1"/>
@@ -414,7 +414,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,6 +442,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -503,6 +509,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7470,7 +7479,7 @@
       <c r="M2" s="5">
         <v>0.99999999998358124</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="13">
         <v>9.4747657568744627E-20</v>
       </c>
       <c r="O2" s="5">
@@ -7566,7 +7575,7 @@
       <c r="AS2" s="5">
         <v>1</v>
       </c>
-      <c r="AT2" s="5">
+      <c r="AT2" s="13">
         <v>5.9034508792565296E-25</v>
       </c>
       <c r="AU2" s="5">
@@ -7602,7 +7611,7 @@
       <c r="BE2" s="5">
         <v>1</v>
       </c>
-      <c r="BF2" s="5">
+      <c r="BF2" s="13">
         <v>1.6529223188613301E-72</v>
       </c>
       <c r="BG2" s="2">
@@ -7679,7 +7688,7 @@
       <c r="U3" s="5">
         <v>1</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V3" s="13">
         <v>3.5029776358737497E-141</v>
       </c>
       <c r="W3" s="5">
@@ -7691,7 +7700,7 @@
       <c r="Y3" s="5">
         <v>1</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3" s="13">
         <v>1.624786414533184E-64</v>
       </c>
       <c r="AA3" s="5">
@@ -7703,7 +7712,7 @@
       <c r="AC3" s="5">
         <v>1</v>
       </c>
-      <c r="AD3" s="5">
+      <c r="AD3" s="13">
         <v>3.47484664341686E-171</v>
       </c>
       <c r="AE3" s="5">
@@ -7775,7 +7784,7 @@
       <c r="BA3" s="5">
         <v>1</v>
       </c>
-      <c r="BB3" s="5">
+      <c r="BB3" s="13">
         <v>1.076185694569204E-197</v>
       </c>
       <c r="BC3" s="5">
@@ -7852,7 +7861,7 @@
       <c r="Q4" s="5">
         <v>0.99999999999999967</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="13">
         <v>9.6669904004877135E-138</v>
       </c>
       <c r="S4" s="5">
@@ -7912,7 +7921,7 @@
       <c r="AK4" s="5">
         <v>1.2100716971802989E-74</v>
       </c>
-      <c r="AL4" s="5">
+      <c r="AL4" s="13">
         <v>1.945343773751816E-81</v>
       </c>
       <c r="AM4" s="5">
@@ -7924,7 +7933,7 @@
       <c r="AO4" s="5">
         <v>1</v>
       </c>
-      <c r="AP4" s="5">
+      <c r="AP4" s="13">
         <v>3.7336137155963601E-153</v>
       </c>
       <c r="AQ4" s="5">
@@ -7948,7 +7957,7 @@
       <c r="AW4" s="5">
         <v>1.4935489606977599E-185</v>
       </c>
-      <c r="AX4" s="5">
+      <c r="AX4" s="13">
         <v>4.7432684194368774E-59</v>
       </c>
       <c r="AY4" s="5">
@@ -8037,7 +8046,7 @@
       <c r="Q5" s="7">
         <v>1</v>
       </c>
-      <c r="R5" s="7">
+      <c r="R5" s="13">
         <v>3.2323281818118338E-88</v>
       </c>
       <c r="S5" s="7">
@@ -8049,7 +8058,7 @@
       <c r="U5" s="7">
         <v>1</v>
       </c>
-      <c r="V5" s="7">
+      <c r="V5" s="13">
         <v>3.9580772877522923E-77</v>
       </c>
       <c r="W5" s="7">
@@ -8073,7 +8082,7 @@
       <c r="AC5" s="7">
         <v>1</v>
       </c>
-      <c r="AD5" s="7">
+      <c r="AD5" s="13">
         <v>6.2672177835785651E-156</v>
       </c>
       <c r="AE5" s="7">
@@ -8109,7 +8118,7 @@
       <c r="AO5" s="7">
         <v>1</v>
       </c>
-      <c r="AP5" s="7">
+      <c r="AP5" s="13">
         <v>7.0536890593392512E-157</v>
       </c>
       <c r="AQ5" s="7">
@@ -8145,7 +8154,7 @@
       <c r="BA5" s="7">
         <v>1</v>
       </c>
-      <c r="BB5" s="7">
+      <c r="BB5" s="13">
         <v>1.569241167657816E-170</v>
       </c>
       <c r="BC5" s="7">
@@ -8395,7 +8404,7 @@
       <c r="M7" s="7">
         <v>1.141199903740764E-77</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="13">
         <v>1.043564636923742E-80</v>
       </c>
       <c r="O7" s="7">
@@ -8431,7 +8440,7 @@
       <c r="Y7" s="7">
         <v>3.6055191761920078E-39</v>
       </c>
-      <c r="Z7" s="7">
+      <c r="Z7" s="13">
         <v>7.0502656550163309E-139</v>
       </c>
       <c r="AA7" s="7">
@@ -8467,7 +8476,7 @@
       <c r="AK7" s="7">
         <v>1.212072519999565E-10</v>
       </c>
-      <c r="AL7" s="7">
+      <c r="AL7" s="13">
         <v>2.761758638022099E-177</v>
       </c>
       <c r="AM7" s="7">
@@ -8503,7 +8512,7 @@
       <c r="AW7" s="7">
         <v>7.0851202982248118E-103</v>
       </c>
-      <c r="AX7" s="7">
+      <c r="AX7" s="13">
         <v>1.2964756745662891E-136</v>
       </c>
       <c r="AY7" s="7">
@@ -8580,7 +8589,7 @@
       <c r="M8" s="9">
         <v>1.601390365178456E-113</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="13">
         <v>3.3886224594721331E-132</v>
       </c>
       <c r="O8" s="9">
@@ -8652,7 +8661,7 @@
       <c r="AK8" s="9">
         <v>1.0339590642827929E-91</v>
       </c>
-      <c r="AL8" s="9">
+      <c r="AL8" s="13">
         <v>1.405935159882604E-149</v>
       </c>
       <c r="AM8" s="9">
@@ -8700,7 +8709,7 @@
       <c r="BA8" s="9">
         <v>1</v>
       </c>
-      <c r="BB8" s="9">
+      <c r="BB8" s="13">
         <v>2.1353120423697011E-38</v>
       </c>
       <c r="BC8" s="9">
@@ -8777,7 +8786,7 @@
       <c r="Q9" s="9">
         <v>1</v>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="13">
         <v>6.2158512455527271E-45</v>
       </c>
       <c r="S9" s="9">
@@ -8813,7 +8822,7 @@
       <c r="AC9" s="9">
         <v>1</v>
       </c>
-      <c r="AD9" s="9">
+      <c r="AD9" s="13">
         <v>1.405935159882604E-149</v>
       </c>
       <c r="AE9" s="9">
@@ -8849,7 +8858,7 @@
       <c r="AO9" s="9">
         <v>1</v>
       </c>
-      <c r="AP9" s="9">
+      <c r="AP9" s="13">
         <v>9.8164763680076484E-111</v>
       </c>
       <c r="AQ9" s="9">
@@ -8873,7 +8882,7 @@
       <c r="AW9" s="9">
         <v>5.5830240707489164E-139</v>
       </c>
-      <c r="AX9" s="9">
+      <c r="AX9" s="13">
         <v>6.7186205577721868E-104</v>
       </c>
       <c r="AY9" s="9">
@@ -8986,7 +8995,7 @@
       <c r="Y10" s="9">
         <v>0.99996765632974705</v>
       </c>
-      <c r="Z10" s="9">
+      <c r="Z10" s="13">
         <v>3.3886224594721331E-132</v>
       </c>
       <c r="AA10" s="9">
@@ -9159,7 +9168,7 @@
       <c r="U11" s="9">
         <v>1</v>
       </c>
-      <c r="V11" s="9">
+      <c r="V11" s="13">
         <v>2.9804535640973499E-16</v>
       </c>
       <c r="W11" s="9">
@@ -9505,7 +9514,7 @@
       <c r="M13" s="11">
         <v>1</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="13">
         <v>1.728284543766001E-194</v>
       </c>
       <c r="O13" s="11">
@@ -9529,7 +9538,7 @@
       <c r="U13" s="11">
         <v>1</v>
       </c>
-      <c r="V13" s="11">
+      <c r="V13" s="13">
         <v>2.9328384174142829E-168</v>
       </c>
       <c r="W13" s="11">
@@ -9541,7 +9550,7 @@
       <c r="Y13" s="11">
         <v>1</v>
       </c>
-      <c r="Z13" s="11">
+      <c r="Z13" s="13">
         <v>1.728284543766001E-194</v>
       </c>
       <c r="AA13" s="11">
@@ -9553,7 +9562,7 @@
       <c r="AC13" s="11">
         <v>1</v>
       </c>
-      <c r="AD13" s="11">
+      <c r="AD13" s="13">
         <v>1.98356930329381E-198</v>
       </c>
       <c r="AE13" s="11">
@@ -9565,7 +9574,7 @@
       <c r="AG13" s="11">
         <v>1</v>
       </c>
-      <c r="AH13" s="11">
+      <c r="AH13" s="13">
         <v>7.3853968232725039E-8</v>
       </c>
       <c r="AI13" s="11">
@@ -9577,7 +9586,7 @@
       <c r="AK13" s="11">
         <v>0.99999993414425803</v>
       </c>
-      <c r="AL13" s="11">
+      <c r="AL13" s="13">
         <v>2.7496109338662921E-133</v>
       </c>
       <c r="AM13" s="11">
@@ -9589,7 +9598,7 @@
       <c r="AO13" s="11">
         <v>1</v>
       </c>
-      <c r="AP13" s="11">
+      <c r="AP13" s="13">
         <v>1.2269891234164789E-271</v>
       </c>
       <c r="AQ13" s="11">
@@ -9601,7 +9610,7 @@
       <c r="AS13" s="11">
         <v>1</v>
       </c>
-      <c r="AT13" s="11">
+      <c r="AT13" s="13">
         <v>1.780879237193481E-140</v>
       </c>
       <c r="AU13" s="11">
@@ -9613,7 +9622,7 @@
       <c r="AW13" s="11">
         <v>1</v>
       </c>
-      <c r="AX13" s="11">
+      <c r="AX13" s="13">
         <v>2.404943654208772E-148</v>
       </c>
       <c r="AY13" s="11">
@@ -9625,7 +9634,7 @@
       <c r="BA13" s="11">
         <v>1</v>
       </c>
-      <c r="BB13" s="11">
+      <c r="BB13" s="13">
         <v>2.9615810909522833E-185</v>
       </c>
       <c r="BC13" s="11">
@@ -9637,7 +9646,7 @@
       <c r="BE13" s="11">
         <v>1</v>
       </c>
-      <c r="BF13" s="11">
+      <c r="BF13" s="13">
         <v>1.4624497416904881E-15</v>
       </c>
       <c r="BG13" s="2">
@@ -9702,7 +9711,7 @@
       <c r="Q14" s="11">
         <v>1</v>
       </c>
-      <c r="R14" s="11">
+      <c r="R14" s="13">
         <v>7.2250008608970368E-179</v>
       </c>
       <c r="S14" s="11">
@@ -9971,7 +9980,7 @@
       <c r="AS15" s="9">
         <v>1</v>
       </c>
-      <c r="AT15" s="9">
+      <c r="AT15" s="13">
         <v>5.5319197747443668E-220</v>
       </c>
       <c r="AU15" s="9">
@@ -10007,7 +10016,7 @@
       <c r="BE15" s="9">
         <v>1</v>
       </c>
-      <c r="BF15" s="9">
+      <c r="BF15" s="13">
         <v>1.0561768432081439E-29</v>
       </c>
       <c r="BG15" s="2">
@@ -10180,7 +10189,7 @@
       <c r="BA16" s="9">
         <v>1</v>
       </c>
-      <c r="BB16" s="9">
+      <c r="BB16" s="13">
         <v>6.1162364502226952E-297</v>
       </c>
       <c r="BC16" s="9">
@@ -10538,7 +10547,7 @@
       <c r="AW18" s="9">
         <v>1</v>
       </c>
-      <c r="AX18" s="9">
+      <c r="AX18" s="13">
         <v>8.376684713988048E-210</v>
       </c>
       <c r="AY18" s="9">
@@ -10615,7 +10624,7 @@
       <c r="M19" s="9">
         <v>1</v>
       </c>
-      <c r="N19" s="9">
+      <c r="N19" s="13">
         <v>1.1881822289344749E-212</v>
       </c>
       <c r="O19" s="9">
@@ -10627,7 +10636,7 @@
       <c r="Q19" s="9">
         <v>1</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R19" s="13">
         <v>1.1881822289344749E-212</v>
       </c>
       <c r="S19" s="9">
@@ -10639,7 +10648,7 @@
       <c r="U19" s="9">
         <v>1</v>
       </c>
-      <c r="V19" s="9">
+      <c r="V19" s="13">
         <v>1.1881822289344749E-212</v>
       </c>
       <c r="W19" s="9">
@@ -10651,7 +10660,7 @@
       <c r="Y19" s="9">
         <v>1</v>
       </c>
-      <c r="Z19" s="9">
+      <c r="Z19" s="13">
         <v>1.1881822289344749E-212</v>
       </c>
       <c r="AA19" s="9">
@@ -10663,7 +10672,7 @@
       <c r="AC19" s="9">
         <v>1</v>
       </c>
-      <c r="AD19" s="9">
+      <c r="AD19" s="13">
         <v>1.1881822289344749E-212</v>
       </c>
       <c r="AE19" s="9">
@@ -10675,7 +10684,7 @@
       <c r="AG19" s="9">
         <v>1</v>
       </c>
-      <c r="AH19" s="9">
+      <c r="AH19" s="13">
         <v>1.1881822289344749E-212</v>
       </c>
       <c r="AI19" s="9">
@@ -10687,7 +10696,7 @@
       <c r="AK19" s="9">
         <v>1</v>
       </c>
-      <c r="AL19" s="9">
+      <c r="AL19" s="13">
         <v>1.1881822289344749E-212</v>
       </c>
       <c r="AM19" s="9">
@@ -10699,7 +10708,7 @@
       <c r="AO19" s="9">
         <v>1</v>
       </c>
-      <c r="AP19" s="9">
+      <c r="AP19" s="13">
         <v>6.1162364502226952E-297</v>
       </c>
       <c r="AQ19" s="9">
